--- a/public/ProdukImport/new_Data_PRODUK_Skripsi_Alat Musik.xlsx
+++ b/public/ProdukImport/new_Data_PRODUK_Skripsi_Alat Musik.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khusus Kuliah ITN\SMSTR 7\SKRIPSI\Data Penjualan Alat Musik (Toko EMC)\Data WEB Produk_Transaksi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A308F7C7-8FBA-45AC-8987-27B193661C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2061D76A-5F27-4B27-AFF7-3DF6E24AE28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{51631238-89C6-4AE4-AC89-2AE0C6458B85}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>Neutrik Jack NC3FXX</t>
   </si>
@@ -107,12 +107,25 @@
   </si>
   <si>
     <t>Srexact Jack Stereo Mini SP110AM-G-C81-BK</t>
+  </si>
+  <si>
+    <t>1,231,200</t>
+  </si>
+  <si>
+    <t>24,000</t>
+  </si>
+  <si>
+    <t>18,000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;Rp&quot;* #,##0.000_-;\-&quot;Rp&quot;* #,##0.000_-;_-&quot;Rp&quot;* &quot;-&quot;???_-;_-@_-"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -202,7 +215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -213,8 +226,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -536,7 +550,7 @@
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -549,8 +563,8 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4">
-        <v>76416</v>
+      <c r="D1" s="5">
+        <v>76.415999999999997</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -563,8 +577,8 @@
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
-        <v>70944</v>
+      <c r="D2" s="5">
+        <v>70.944000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -577,8 +591,8 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4">
-        <v>24000</v>
+      <c r="D3" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -591,8 +605,8 @@
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="4">
-        <v>18000</v>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -605,8 +619,8 @@
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4">
-        <v>101232</v>
+      <c r="D5" s="5">
+        <v>101.232</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -619,8 +633,8 @@
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4">
-        <v>88578</v>
+      <c r="D6" s="5">
+        <v>88.578000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -633,8 +647,8 @@
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="5">
-        <v>1231200.1007999999</v>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -647,8 +661,8 @@
       <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="4">
-        <v>14763</v>
+      <c r="D8" s="5">
+        <v>14.763</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -662,7 +676,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="5">
-        <v>25097.1</v>
+        <v>25.097000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -676,7 +690,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="5">
-        <v>24358.95</v>
+        <v>24.358000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -690,7 +704,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="5">
-        <v>14726.088</v>
+        <v>14.726000000000001</v>
       </c>
     </row>
   </sheetData>
